--- a/HW06_API_Test_Cases_and_Summary.xlsx
+++ b/HW06_API_Test_Cases_and_Summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1404" uniqueCount="587">
   <si>
     <t>BÁO CÁO TỔNG HỢP KIỂM THỬ API - HW06 (API TESTING SUMMARY)</t>
   </si>
@@ -209,7 +209,7 @@
     <t>0.0% Tuyệt đối chính xác</t>
   </si>
   <si>
-    <t>Số Test Cases Mở Rộng bởi Con người</t>
+    <t>Số Test Cases Mở Rộng Thêm (EXT)</t>
   </si>
   <si>
     <t>Bao phủ 100% điểm mù của AI</t>
@@ -578,6 +578,9 @@
     <t>search=SEC-05: SQL Injection Stacked Queries ('; DROP TABLE)</t>
   </si>
   <si>
+    <t>Kiểm thử Stacked Queries phá hoại</t>
+  </si>
+  <si>
     <t>TC_FR05_26</t>
   </si>
   <si>
@@ -632,6 +635,9 @@
     <t>Security HPP OK</t>
   </si>
   <si>
+    <t>Kiểm thử HTTP Parameter Pollution</t>
+  </si>
+  <si>
     <t>TC_FR05_30</t>
   </si>
   <si>
@@ -755,400 +761,316 @@
     <t>Functional Edge OK</t>
   </si>
   <si>
-    <t>TC_FR05_EXT01</t>
-  </si>
-  <si>
-    <t>Security SQLi</t>
-  </si>
-  <si>
-    <t>/api/products?search=iPhone'</t>
-  </si>
-  <si>
-    <t>search=iPhone'</t>
-  </si>
-  <si>
-    <t>200 / 400</t>
-  </si>
-  <si>
-    <t>Bắt lỗi cú pháp SQL an toàn, không trả về trang lỗi HTML 500 rò rỉ CSDL</t>
+    <t>INCOMPLETE</t>
+  </si>
+  <si>
+    <t>Request Payload (JSON)</t>
+  </si>
+  <si>
+    <t>TC_FR08_01</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>/api/checkout</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Happy Path - Valid checkout with valid user token and cart\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>application/json</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Phát hiện lỗi B003 (total_amount = 0)</t>
+  </si>
+  <si>
+    <t>TC_FR08_02</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Valid checkout with Vietnamese UTF-8 address\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_03</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Valid checkout with 2 decimal precision amount\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_04</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Valid checkout with international address format\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_05</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Valid checkout with large integer amount\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_06</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"BVA - total_amount equals 0 (Boundary 0)\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_07</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"BVA - total_amount is negative -1\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_08</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"BVA - total_amount is large negative -999999.99\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_09</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"BVA - total_amount is minimum positive 0.01\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_10</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"BVA - total_amount has 3 decimal places 100.555\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_11</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - total_amount is null\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{""total_amount"": null</t>
+  </si>
+  <si>
+    <t>TC_FR08_12</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - total_amount is empty string\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{""total_amount"": """"</t>
+  </si>
+  <si>
+    <t>TC_FR08_13</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - total_amount is text string free\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{""total_amount"": ""free""</t>
+  </si>
+  <si>
+    <t>TC_FR08_14</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - total_amount is numeric string 100.50 instead of number\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{""total_amount"": ""100.50""</t>
+  </si>
+  <si>
+    <t>TC_FR08_15</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - total_amount is boolean true\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{""total_amount"": true</t>
+  </si>
+  <si>
+    <t>TC_FR08_16</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - total_amount is object {}\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{""total_amount"": {}</t>
+  </si>
+  <si>
+    <t>TC_FR08_17</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - total_amount field is missing\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{""shipping_address"": ""123 Le Loi</t>
+  </si>
+  <si>
+    <t>TC_FR08_18</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - shipping_address is empty string\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_19</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - shipping_address is only whitespace\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_20</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - shipping_address is null\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{""total_amount"": 100</t>
+  </si>
+  <si>
+    <t>TC_FR08_21</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - shipping_address field is missing\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{""total_amount"": 100}"</t>
+  </si>
+  <si>
+    <t>TC_FR08_22</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - shipping_address is number 12345\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_23</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - shipping_address is boolean true\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_24</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - shipping_address is object {}\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_25</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"EP - shipping_address is array []\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_26</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"BVA - shipping_address is 1 char (too short)\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_27</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"BVA - shipping_address is maximum length 500 chars\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_28</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Security SEC-02 - Missing Authorization header\"","shipping_address":"missing"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_29</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Security SEC-02 - Empty Bearer token\"","shipping_address":"empty"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_30</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Security SEC-02 - Invalid signature JWT token\"","shipping_address":"invalid"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_31</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Security SEC-02 - Authorization header without Bearer prefix\"","shipping_address":"no_bearer"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_32</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Security SEC-02 - Basic Auth instead of Bearer token\"","shipping_address":"basic"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_33</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Security SEC-04 - Stored XSS payload in shipping_address\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_34</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Security SEC-05 - SQL Injection in shipping_address\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_35</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Security SEC-05 - SQL DROP TABLE in shipping_address\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_36</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Business Logic - Checkout with empty cart\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_37</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Business Logic - Price tampering total amount mismatch\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_38</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Edge Case - Empty JSON body {}\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>"{}"</t>
+  </si>
+  <si>
+    <t>TC_FR08_39</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Security - Mass Assignment privilege tampering status and user_id\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>TC_FR08_40</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Schema - Content-Type text/plain instead of JSON\"","shipping_address":"valid_user"}</t>
+  </si>
+  <si>
+    <t>text/plain</t>
+  </si>
+  <si>
+    <t>"total_amount=100&amp;shipping_address=HCM"</t>
+  </si>
+  <si>
+    <t>TC_FR08_EXT01</t>
+  </si>
+  <si>
+    <t>{"total_amount":"\"Extension - Double checkout race condition\"","shipping_address":"valid_user"}</t>
   </si>
   <si>
     <t>HUMAN EXT</t>
-  </si>
-  <si>
-    <t>TC_FR05_EXT02</t>
-  </si>
-  <si>
-    <t>/api/products?search=' UNION SELECT id,name,email,password,5,6 FROM users--</t>
-  </si>
-  <si>
-    <t>search=' UNION SELECT...</t>
-  </si>
-  <si>
-    <t>Chặn trích xuất trái phép tài khoản quản trị và mật khẩu từ bảng users</t>
-  </si>
-  <si>
-    <t>TC_FR05_EXT03</t>
-  </si>
-  <si>
-    <t>Security Destructive</t>
-  </si>
-  <si>
-    <t>/api/products?search=iPhone'; DROP TABLE products;--</t>
-  </si>
-  <si>
-    <t>search=iPhone'; DROP...</t>
-  </si>
-  <si>
-    <t>Từ chối thực thi Stacked Queries phá hoại cơ sở dữ liệu</t>
-  </si>
-  <si>
-    <t>Bảo vệ an toàn SQLite chống phá hoại</t>
-  </si>
-  <si>
-    <t>TC_FR05_EXT04</t>
-  </si>
-  <si>
-    <t>Security HPP</t>
-  </si>
-  <si>
-    <t>/api/products?search=iPhone&amp;search=Samsung</t>
-  </si>
-  <si>
-    <t>search=iPhone&amp;search=Samsung</t>
-  </si>
-  <si>
-    <t>200 OK</t>
-  </si>
-  <si>
-    <t>Xử lý an toàn mảng tham số trùng lặp (HTTP Parameter Pollution)</t>
-  </si>
-  <si>
-    <t>Kiểm soát chặt chẽ kiểu dữ liệu query string</t>
-  </si>
-  <si>
-    <t>TC_FR05_EXT05</t>
-  </si>
-  <si>
-    <t>Schema &amp; Type</t>
-  </si>
-  <si>
-    <t>/api/products</t>
-  </si>
-  <si>
-    <t>(None)</t>
-  </si>
-  <si>
-    <t>Kiểm định chặt chẽ trường price của tất cả sản phẩm luôn là kiểu number</t>
-  </si>
-  <si>
-    <t>Phát hiện lỗi ép kiểu ngầm định string trên id chẵn</t>
-  </si>
-  <si>
-    <t>Request Payload (JSON)</t>
-  </si>
-  <si>
-    <t>TC_FR08_01</t>
-  </si>
-  <si>
-    <t>false</t>
-  </si>
-  <si>
-    <t>POST</t>
-  </si>
-  <si>
-    <t>/api/checkout</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Happy Path - Valid checkout with valid user token and cart\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>application/json</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Phát hiện lỗi B003 (total_amount = 0)</t>
-  </si>
-  <si>
-    <t>TC_FR08_02</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Valid checkout with Vietnamese UTF-8 address\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_03</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Valid checkout with 2 decimal precision amount\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_04</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Valid checkout with international address format\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_05</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Valid checkout with large integer amount\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_06</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"BVA - total_amount equals 0 (Boundary 0)\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_07</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"BVA - total_amount is negative -1\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_08</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"BVA - total_amount is large negative -999999.99\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_09</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"BVA - total_amount is minimum positive 0.01\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_10</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"BVA - total_amount has 3 decimal places 100.555\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_11</t>
-  </si>
-  <si>
-    <t>true</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - total_amount is null\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{""total_amount"": null</t>
-  </si>
-  <si>
-    <t>TC_FR08_12</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - total_amount is empty string\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{""total_amount"": """"</t>
-  </si>
-  <si>
-    <t>TC_FR08_13</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - total_amount is text string free\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{""total_amount"": ""free""</t>
-  </si>
-  <si>
-    <t>TC_FR08_14</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - total_amount is numeric string 100.50 instead of number\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{""total_amount"": ""100.50""</t>
-  </si>
-  <si>
-    <t>TC_FR08_15</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - total_amount is boolean true\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{""total_amount"": true</t>
-  </si>
-  <si>
-    <t>TC_FR08_16</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - total_amount is object {}\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{""total_amount"": {}</t>
-  </si>
-  <si>
-    <t>TC_FR08_17</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - total_amount field is missing\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{""shipping_address"": ""123 Le Loi</t>
-  </si>
-  <si>
-    <t>TC_FR08_18</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - shipping_address is empty string\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_19</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - shipping_address is only whitespace\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_20</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - shipping_address is null\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{""total_amount"": 100</t>
-  </si>
-  <si>
-    <t>TC_FR08_21</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - shipping_address field is missing\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{""total_amount"": 100}"</t>
-  </si>
-  <si>
-    <t>TC_FR08_22</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - shipping_address is number 12345\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_23</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - shipping_address is boolean true\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_24</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - shipping_address is object {}\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_25</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"EP - shipping_address is array []\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_26</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"BVA - shipping_address is 1 char (too short)\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_27</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"BVA - shipping_address is maximum length 500 chars\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_28</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Security SEC-02 - Missing Authorization header\"","shipping_address":"missing"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_29</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Security SEC-02 - Empty Bearer token\"","shipping_address":"empty"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_30</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Security SEC-02 - Invalid signature JWT token\"","shipping_address":"invalid"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_31</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Security SEC-02 - Authorization header without Bearer prefix\"","shipping_address":"no_bearer"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_32</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Security SEC-02 - Basic Auth instead of Bearer token\"","shipping_address":"basic"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_33</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Security SEC-04 - Stored XSS payload in shipping_address\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_34</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Security SEC-05 - SQL Injection in shipping_address\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_35</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Security SEC-05 - SQL DROP TABLE in shipping_address\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_36</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Business Logic - Checkout with empty cart\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_37</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Business Logic - Price tampering total amount mismatch\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_38</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Edge Case - Empty JSON body {}\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>"{}"</t>
-  </si>
-  <si>
-    <t>TC_FR08_39</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Security - Mass Assignment privilege tampering status and user_id\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>TC_FR08_40</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Schema - Content-Type text/plain instead of JSON\"","shipping_address":"valid_user"}</t>
-  </si>
-  <si>
-    <t>text/plain</t>
-  </si>
-  <si>
-    <t>"total_amount=100&amp;shipping_address=HCM"</t>
-  </si>
-  <si>
-    <t>TC_FR08_EXT01</t>
-  </si>
-  <si>
-    <t>{"total_amount":"\"Extension - Double checkout race condition\"","shipping_address":"valid_user"}</t>
   </si>
   <si>
     <t>TC_FR08_EXT02</t>
@@ -2414,10 +2336,10 @@
         <v>40</v>
       </c>
       <c r="E10" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F10" s="6">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G10" s="6" t="s">
         <v>22</v>
@@ -2474,10 +2396,10 @@
         <v>120</v>
       </c>
       <c r="E13" s="9">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F13" s="9">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>31</v>
@@ -2688,7 +2610,7 @@
         <v>64</v>
       </c>
       <c r="C27" s="6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D27" s="6">
         <v>5</v>
@@ -2697,7 +2619,7 @@
         <v>5</v>
       </c>
       <c r="F27" s="6">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G27" s="6" t="s">
         <v>65</v>
@@ -2717,7 +2639,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -3482,24 +3404,24 @@
         <v>82</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>83</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>77</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>166</v>
@@ -3516,22 +3438,22 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G28" s="6" t="s">
         <v>81</v>
@@ -3545,22 +3467,22 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>77</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>81</v>
@@ -3574,22 +3496,22 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G30" s="6" t="s">
         <v>81</v>
@@ -3598,27 +3520,27 @@
         <v>82</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>83</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>77</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>81</v>
@@ -3632,7 +3554,7 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>76</v>
@@ -3641,13 +3563,13 @@
         <v>77</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>81</v>
@@ -3661,7 +3583,7 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>76</v>
@@ -3670,13 +3592,13 @@
         <v>77</v>
       </c>
       <c r="D33" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>215</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>213</v>
       </c>
       <c r="G33" s="7" t="s">
         <v>81</v>
@@ -3690,7 +3612,7 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>76</v>
@@ -3699,13 +3621,13 @@
         <v>77</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>81</v>
@@ -3719,7 +3641,7 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>76</v>
@@ -3728,13 +3650,13 @@
         <v>77</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>81</v>
@@ -3748,7 +3670,7 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>76</v>
@@ -3757,13 +3679,13 @@
         <v>77</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="G36" s="6" t="s">
         <v>81</v>
@@ -3777,7 +3699,7 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>76</v>
@@ -3786,13 +3708,13 @@
         <v>77</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>81</v>
@@ -3806,7 +3728,7 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>76</v>
@@ -3815,13 +3737,13 @@
         <v>77</v>
       </c>
       <c r="D38" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="G38" s="6" t="s">
         <v>81</v>
@@ -3835,7 +3757,7 @@
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>76</v>
@@ -3844,13 +3766,13 @@
         <v>77</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>81</v>
@@ -3864,7 +3786,7 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>76</v>
@@ -3873,13 +3795,13 @@
         <v>77</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>81</v>
@@ -3893,176 +3815,31 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>77</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="G41" s="7" t="s">
         <v>81</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>83</v>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>247</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>255</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>274</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -4101,7 +3878,7 @@
         <v>69</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>71</v>
@@ -4118,1307 +3895,1307 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>277</v>
+        <v>250</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>285</v>
+        <v>258</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>292</v>
+        <v>265</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>294</v>
+        <v>267</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>295</v>
+        <v>268</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>297</v>
+        <v>270</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>298</v>
+        <v>271</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>300</v>
+        <v>273</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>301</v>
+        <v>274</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>303</v>
+        <v>276</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>306</v>
-      </c>
       <c r="H12" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>308</v>
+        <v>281</v>
       </c>
       <c r="F13" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>309</v>
-      </c>
       <c r="H13" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>310</v>
+        <v>283</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>311</v>
+        <v>284</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>312</v>
+        <v>285</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>314</v>
+        <v>287</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>315</v>
+        <v>288</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>316</v>
+        <v>289</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>317</v>
+        <v>290</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>318</v>
+        <v>291</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>319</v>
+        <v>292</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>321</v>
+        <v>294</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>323</v>
+        <v>296</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>325</v>
+        <v>298</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>326</v>
+        <v>299</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>327</v>
+        <v>300</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>328</v>
+        <v>301</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>329</v>
+        <v>302</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G21" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C21" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="H21" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>332</v>
+        <v>305</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>333</v>
+        <v>306</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>334</v>
+        <v>307</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>335</v>
+        <v>308</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="H23" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="B24" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>331</v>
-      </c>
       <c r="H24" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="H25" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>341</v>
+        <v>314</v>
       </c>
       <c r="B26" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>342</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>331</v>
-      </c>
       <c r="H26" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>343</v>
+        <v>316</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>344</v>
+        <v>317</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>345</v>
+        <v>318</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>346</v>
+        <v>319</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>347</v>
+        <v>320</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>348</v>
+        <v>321</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I30" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>352</v>
+        <v>325</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>353</v>
+        <v>326</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>354</v>
+        <v>327</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>355</v>
+        <v>328</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>358</v>
+        <v>331</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I34" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>359</v>
+        <v>332</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>360</v>
+        <v>333</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>361</v>
+        <v>334</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>362</v>
+        <v>335</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I36" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>363</v>
+        <v>336</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>364</v>
+        <v>337</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>365</v>
+        <v>338</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>366</v>
+        <v>339</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I38" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>367</v>
+        <v>340</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>368</v>
+        <v>341</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>370</v>
+        <v>343</v>
       </c>
       <c r="B40" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>331</v>
-      </c>
       <c r="H40" s="6" t="s">
         <v>82</v>
       </c>
       <c r="I40" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>372</v>
+        <v>345</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>304</v>
+        <v>277</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>373</v>
+        <v>346</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>374</v>
+        <v>347</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>375</v>
+        <v>348</v>
       </c>
       <c r="H41" s="7" t="s">
         <v>82</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>376</v>
+        <v>349</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>377</v>
+        <v>350</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>378</v>
+        <v>352</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>381</v>
+        <v>355</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>382</v>
+        <v>356</v>
       </c>
       <c r="B45" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="G45" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C45" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>331</v>
-      </c>
       <c r="H45" s="7" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>384</v>
+        <v>358</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>279</v>
+        <v>252</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>280</v>
+        <v>253</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>282</v>
+        <v>255</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>284</v>
+        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -5458,10 +5235,10 @@
         <v>69</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>276</v>
+        <v>249</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>71</v>
@@ -5478,25 +5255,25 @@
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>387</v>
+        <v>361</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>392</v>
+        <v>366</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>81</v>
@@ -5510,28 +5287,28 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>394</v>
+        <v>368</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>395</v>
+        <v>369</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>396</v>
+        <v>370</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>397</v>
+        <v>371</v>
       </c>
       <c r="I3" s="7" t="s">
         <v>82</v>
@@ -5542,60 +5319,60 @@
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>398</v>
+        <v>372</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>399</v>
+        <v>373</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>400</v>
+        <v>374</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I4" s="6" t="s">
         <v>82</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>403</v>
+        <v>377</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>404</v>
+        <v>378</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>405</v>
+        <v>379</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I5" s="7" t="s">
         <v>82</v>
@@ -5606,28 +5383,28 @@
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>406</v>
+        <v>380</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I6" s="6" t="s">
         <v>82</v>
@@ -5638,28 +5415,28 @@
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>410</v>
+        <v>384</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>82</v>
@@ -5670,28 +5447,28 @@
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>412</v>
+        <v>386</v>
       </c>
       <c r="B8" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>388</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>389</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>391</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>413</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>414</v>
-      </c>
       <c r="H8" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>82</v>
@@ -5702,28 +5479,28 @@
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>415</v>
+        <v>389</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>418</v>
+        <v>392</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>82</v>
@@ -5734,28 +5511,28 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>420</v>
+        <v>394</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>422</v>
+        <v>396</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>423</v>
+        <v>397</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I10" s="6" t="s">
         <v>82</v>
@@ -5766,28 +5543,28 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>424</v>
+        <v>398</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>426</v>
+        <v>400</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>427</v>
+        <v>401</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>82</v>
@@ -5798,28 +5575,28 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>428</v>
+        <v>402</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>429</v>
+        <v>403</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>430</v>
+        <v>404</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>431</v>
+        <v>405</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>82</v>
@@ -5830,28 +5607,28 @@
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>432</v>
+        <v>406</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>416</v>
+        <v>390</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>433</v>
+        <v>407</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>434</v>
+        <v>408</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I13" s="7" t="s">
         <v>82</v>
@@ -5862,25 +5639,25 @@
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>436</v>
+        <v>410</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>438</v>
+        <v>412</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>439</v>
+        <v>413</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>81</v>
@@ -5894,25 +5671,25 @@
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>440</v>
+        <v>414</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>442</v>
+        <v>416</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>443</v>
+        <v>417</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>81</v>
@@ -5926,25 +5703,25 @@
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>444</v>
+        <v>418</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>81</v>
@@ -5958,25 +5735,25 @@
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>448</v>
+        <v>422</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>449</v>
+        <v>423</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>450</v>
+        <v>424</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>81</v>
@@ -5990,25 +5767,25 @@
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>451</v>
+        <v>425</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>453</v>
+        <v>427</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>454</v>
+        <v>428</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>81</v>
@@ -6022,28 +5799,28 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>455</v>
+        <v>429</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>456</v>
+        <v>430</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>457</v>
+        <v>431</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>82</v>
@@ -6054,28 +5831,28 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>445</v>
+        <v>419</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>459</v>
+        <v>433</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>460</v>
+        <v>434</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>82</v>
@@ -6086,28 +5863,28 @@
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>461</v>
+        <v>435</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>436</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="E21" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>463</v>
-      </c>
       <c r="G21" s="7" t="s">
-        <v>464</v>
+        <v>438</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>82</v>
@@ -6118,28 +5895,28 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>465</v>
+        <v>439</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>466</v>
+        <v>440</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>467</v>
+        <v>441</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I22" s="6" t="s">
         <v>82</v>
@@ -6150,28 +5927,28 @@
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>468</v>
+        <v>442</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>469</v>
+        <v>443</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>470</v>
+        <v>444</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>82</v>
@@ -6182,28 +5959,28 @@
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>471</v>
+        <v>445</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>441</v>
+        <v>415</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>472</v>
+        <v>446</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>473</v>
+        <v>447</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I24" s="6" t="s">
         <v>82</v>
@@ -6214,28 +5991,28 @@
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>474</v>
+        <v>448</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>437</v>
+        <v>411</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>462</v>
+        <v>436</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>475</v>
+        <v>449</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>476</v>
+        <v>450</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>82</v>
@@ -6246,28 +6023,28 @@
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>477</v>
+        <v>451</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>478</v>
+        <v>452</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>480</v>
+        <v>454</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>481</v>
+        <v>455</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="I26" s="6" t="s">
         <v>82</v>
@@ -6278,28 +6055,28 @@
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>483</v>
+        <v>457</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>484</v>
+        <v>458</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>485</v>
+        <v>459</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>486</v>
+        <v>460</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>482</v>
+        <v>456</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>82</v>
@@ -6310,28 +6087,28 @@
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>487</v>
+        <v>461</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>488</v>
+        <v>462</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>490</v>
+        <v>464</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="I28" s="6" t="s">
         <v>82</v>
@@ -6342,28 +6119,28 @@
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>492</v>
+        <v>466</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>493</v>
+        <v>467</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>479</v>
+        <v>453</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>494</v>
+        <v>468</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>82</v>
@@ -6374,60 +6151,60 @@
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>496</v>
+        <v>470</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>499</v>
+        <v>473</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>500</v>
+        <v>474</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="I30" s="6" t="s">
         <v>82</v>
       </c>
       <c r="J30" s="6" t="s">
-        <v>501</v>
+        <v>475</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>502</v>
+        <v>476</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>498</v>
+        <v>472</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>504</v>
+        <v>478</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="I31" s="7" t="s">
         <v>82</v>
@@ -6438,28 +6215,28 @@
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
-        <v>505</v>
+        <v>479</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>506</v>
+        <v>480</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>507</v>
+        <v>481</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I32" s="6" t="s">
         <v>82</v>
@@ -6470,28 +6247,28 @@
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>512</v>
+        <v>486</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>513</v>
+        <v>487</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>82</v>
@@ -6502,28 +6279,28 @@
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
-        <v>515</v>
+        <v>489</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>511</v>
+        <v>485</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>516</v>
+        <v>490</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I34" s="6" t="s">
         <v>82</v>
@@ -6534,28 +6311,28 @@
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>518</v>
+        <v>492</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>519</v>
+        <v>493</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>520</v>
+        <v>494</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>521</v>
+        <v>495</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>522</v>
+        <v>496</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>523</v>
+        <v>497</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>82</v>
@@ -6566,25 +6343,25 @@
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
-        <v>524</v>
+        <v>498</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>77</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>81</v>
@@ -6598,25 +6375,25 @@
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>527</v>
+        <v>501</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>77</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>528</v>
+        <v>502</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>81</v>
@@ -6630,25 +6407,25 @@
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>530</v>
+        <v>504</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>495</v>
+        <v>469</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>81</v>
@@ -6662,28 +6439,28 @@
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>531</v>
+        <v>505</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>525</v>
+        <v>499</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>532</v>
+        <v>506</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>533</v>
+        <v>507</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>534</v>
+        <v>508</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>82</v>
@@ -6694,28 +6471,28 @@
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
-        <v>535</v>
+        <v>509</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>536</v>
+        <v>510</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>537</v>
+        <v>511</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>538</v>
+        <v>512</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>539</v>
+        <v>513</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I40" s="6" t="s">
         <v>82</v>
@@ -6726,28 +6503,28 @@
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>540</v>
+        <v>514</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>541</v>
+        <v>515</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>369</v>
+        <v>342</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>542</v>
+        <v>516</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>543</v>
+        <v>517</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>82</v>
@@ -6758,63 +6535,63 @@
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
-        <v>544</v>
+        <v>518</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>452</v>
+        <v>426</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>546</v>
+        <v>520</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>547</v>
+        <v>521</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I42" s="6" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="J42" s="6" t="s">
-        <v>548</v>
+        <v>522</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>549</v>
+        <v>523</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>550</v>
+        <v>524</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>393</v>
+        <v>367</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="J43" s="7" t="s">
         <v>83</v>
@@ -6822,63 +6599,63 @@
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
-        <v>551</v>
+        <v>525</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>552</v>
+        <v>526</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>553</v>
+        <v>527</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>419</v>
+        <v>393</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I44" s="6" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="J44" s="6" t="s">
-        <v>402</v>
+        <v>376</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>554</v>
+        <v>528</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>497</v>
+        <v>471</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>555</v>
+        <v>529</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>514</v>
+        <v>488</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>491</v>
+        <v>465</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="J45" s="7" t="s">
         <v>83</v>
@@ -6886,31 +6663,31 @@
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>556</v>
+        <v>530</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>388</v>
+        <v>362</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>389</v>
+        <v>363</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>391</v>
+        <v>365</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>557</v>
+        <v>531</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>558</v>
+        <v>532</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>401</v>
+        <v>375</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>252</v>
+        <v>351</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>83</v>
@@ -6938,292 +6715,292 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>559</v>
+        <v>533</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>560</v>
+        <v>534</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>561</v>
+        <v>535</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>562</v>
+        <v>536</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>563</v>
+        <v>537</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>564</v>
+        <v>538</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>565</v>
+        <v>539</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>566</v>
+        <v>540</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>567</v>
+        <v>541</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>568</v>
+        <v>542</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>569</v>
+        <v>543</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>570</v>
+        <v>544</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>576</v>
+        <v>550</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>577</v>
+        <v>551</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>578</v>
+        <v>552</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>571</v>
+        <v>545</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>581</v>
+        <v>555</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>582</v>
+        <v>556</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>583</v>
+        <v>557</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>584</v>
+        <v>558</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>586</v>
+        <v>560</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>587</v>
+        <v>561</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>588</v>
+        <v>562</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>589</v>
+        <v>563</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>590</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>591</v>
+        <v>565</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>593</v>
+        <v>567</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>594</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>595</v>
+        <v>569</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>596</v>
+        <v>570</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>597</v>
+        <v>571</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>585</v>
+        <v>559</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>598</v>
+        <v>572</v>
       </c>
       <c r="F7" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>573</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>600</v>
+        <v>574</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>601</v>
+        <v>575</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>602</v>
+        <v>576</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>603</v>
+        <v>577</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>572</v>
+        <v>546</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>604</v>
+        <v>578</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>605</v>
+        <v>579</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>606</v>
+        <v>580</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>607</v>
+        <v>581</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>603</v>
+        <v>577</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>580</v>
+        <v>554</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>608</v>
+        <v>582</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>609</v>
+        <v>583</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>610</v>
+        <v>584</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>611</v>
+        <v>585</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>603</v>
+        <v>577</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>598</v>
+        <v>572</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>573</v>
+        <v>547</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>574</v>
+        <v>548</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>575</v>
+        <v>549</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>612</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>

--- a/HW06_API_Test_Cases_and_Summary.xlsx
+++ b/HW06_API_Test_Cases_and_Summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1276" uniqueCount="703">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1409" uniqueCount="740">
   <si>
     <t>BÁO CÁO TỔNG HỢP KIỂM THỬ API - HW06 (API TESTING SUMMARY)</t>
   </si>
@@ -230,6 +230,9 @@
     <t>Kết quả mong đợi (Expected Result)</t>
   </si>
   <si>
+    <t>Kết quả thực tế (Actual Result)</t>
+  </si>
+  <si>
     <t>Đánh giá AI (Verdict)</t>
   </si>
   <si>
@@ -251,6 +254,9 @@
     <t>Trả về mảng JSON chứa tất cả sản phẩm trong CSDL.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Trả về mảng JSON sản phẩm đúng kỳ vọng)</t>
+  </si>
+  <si>
     <t>VALID</t>
   </si>
   <si>
@@ -518,6 +524,9 @@
     <t>Không bị lỗi cú pháp SQL dẫn đến 500 Database Error HTML.</t>
   </si>
   <si>
+    <t>HTTP 500 Internal Server Error (Trả về trang HTML lỗi CSDL SQLite - Lỗi B002)</t>
+  </si>
+  <si>
     <t>Phát hiện lỗi bẻ gãy cú pháp SQL dẫn đến sập máy chủ.</t>
   </si>
   <si>
@@ -530,6 +539,9 @@
     <t>Tuyệt đối không để lộ danh sách email/mật khẩu bảng users.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (SQLi thành công, dump toàn bộ password/email bảng users - Lỗ hổng B001)</t>
+  </si>
+  <si>
     <t>Phát hiện lỗ hổng SQLi Union-based trích xuất CSDL nhạy cảm.</t>
   </si>
   <si>
@@ -722,6 +734,9 @@
     <t>Từ chối tạo sản phẩm khi không có quyền Admin.</t>
   </si>
   <si>
+    <t>HTTP 401/403 (Từ chối truy cập đúng phân quyền)</t>
+  </si>
+  <si>
     <t>Kiểm thử phân quyền RBAC ngăn chặn thao tác ghi trái phép.</t>
   </si>
   <si>
@@ -740,6 +755,9 @@
     <t>Báo lỗi không hỗ trợ DELETE trên root collection.</t>
   </si>
   <si>
+    <t>HTTP 404/405 (Báo lỗi endpoint/method không tồn tại)</t>
+  </si>
+  <si>
     <t>Kiểm thử Negative Testing phương thức HTTP không được hỗ trợ.</t>
   </si>
   <si>
@@ -785,6 +803,9 @@
     <t>Tạo đơn hàng thành công, trả về orderId &gt; 0.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Tạo đơn hàng thành công, trả về orderId &gt; 0)</t>
+  </si>
+  <si>
     <t>Bao phủ Happy Path luồng đặt hàng chuẩn với đầy đủ điều kiện.</t>
   </si>
   <si>
@@ -857,6 +878,9 @@
     <t>Từ chối đơn hàng có giá trị 0 đồng.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Tạo đơn hàng với total_amount = 0 - Lỗi B003)</t>
+  </si>
+  <si>
     <t>Kiểm thử giá trị biên 0 đồng (phát hiện lỗi B003).</t>
   </si>
   <si>
@@ -869,6 +893,9 @@
     <t>Từ chối số tiền âm.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Tạo đơn hàng với total_amount = -1 - Lỗi B003)</t>
+  </si>
+  <si>
     <t>Kiểm thử giá trị biên số âm (phát hiện lỗi B003).</t>
   </si>
   <si>
@@ -881,6 +908,9 @@
     <t>Từ chối số tiền âm cực lớn.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Tạo đơn hàng với total_amount = -999999.99 - Lỗi B003)</t>
+  </si>
+  <si>
     <t>Kiểm thử số âm cực hạn.</t>
   </si>
   <si>
@@ -905,6 +935,9 @@
     <t>Kiểm tra validation định dạng tiền tệ tối đa 2 chữ số lẻ.</t>
   </si>
   <si>
+    <t>HTTP 400 Bad Request (Báo lỗi validation dữ liệu đầu vào)</t>
+  </si>
+  <si>
     <t>Kiểm thử độ chính xác định dạng tiền tệ (precision).</t>
   </si>
   <si>
@@ -1007,6 +1040,9 @@
     <t>Báo lỗi địa chỉ giao hàng không được để trống.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Chấp nhận địa chỉ rỗng - Lỗi B004)</t>
+  </si>
+  <si>
     <t>Phân vùng kiểm tra địa chỉ rỗng (phát hiện lỗi B004).</t>
   </si>
   <si>
@@ -1019,6 +1055,9 @@
     <t>Báo lỗi chuỗi chỉ chứa whitespace không hợp lệ.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Chấp nhận địa chỉ chỉ chứa khoảng trắng - Lỗi B004)</t>
+  </si>
+  <si>
     <t>Phân vùng kiểm tra địa chỉ chỉ chứa khoảng trắng (lỗi B004).</t>
   </si>
   <si>
@@ -1136,6 +1175,9 @@
     <t>Trả về mã lỗi 401 (error: "Access token required").</t>
   </si>
   <si>
+    <t>HTTP 401 Unauthorized (Báo lỗi thiếu token)</t>
+  </si>
+  <si>
     <t>Kiểm tra xác thực khi thiếu hoàn toàn Authorization Header.</t>
   </si>
   <si>
@@ -1166,6 +1208,9 @@
     <t>Trả về mã lỗi 403 (error: "Invalid or expired token").</t>
   </si>
   <si>
+    <t>HTTP 403 Forbidden (Báo lỗi token không hợp lệ)</t>
+  </si>
+  <si>
     <t>Kiểm tra từ chối token giả mạo/sai chữ ký mật mã.</t>
   </si>
   <si>
@@ -1241,6 +1286,9 @@
     <t>Từ chối tạo đơn hàng khi người dùng chưa có sản phẩm trong giỏ.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Cho phép checkout khi giỏ hàng rỗng - Lỗi B005)</t>
+  </si>
+  <si>
     <t>AI sinh thiếu pre-request dọn giỏ hàng để thiết lập trạng thái rỗng.</t>
   </si>
   <si>
@@ -1256,6 +1304,9 @@
     <t>Backend phải tự tính toán lại tổng tiền từ giỏ hàng.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Không tính toán lại tổng tiền từ giỏ hàng - Lỗi B005)</t>
+  </si>
+  <si>
     <t>AI sinh thiếu logic đối chiếu tổng tiền tính toán từ giỏ hàng thực tế.</t>
   </si>
   <si>
@@ -1302,6 +1353,9 @@
   </si>
   <si>
     <t>Báo lỗi định dạng Content-Type không được hỗ trợ.</t>
+  </si>
+  <si>
+    <t>HTTP 500 Internal Server Error (Sập server trả về HTML khi nhận Content-Type text/plain - Lỗi B006)</t>
   </si>
   <si>
     <t>Kiểm định Header Content-Type (phát hiện lỗi máy chủ B006).</t>
@@ -1320,7 +1374,10 @@
 *</t>
   </si>
   <si>
-    <t>HUMAN EXT</t>
+    <t>HTTP 200 OK (Double checkout tạo 2 đơn hàng song song do Race Condition)</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Lý do AI bỏ sót: * AI thông thường chỉ sinh ca đơn lẻ, bỏ qua kịch bản kiểm thử tương tranh (Race Condition).</t>
@@ -1337,6 +1394,9 @@
   <si>
     <t xml:space="preserve">Tràn số thực dấu phẩy động (MAX_SAFE_INTEGER + 1) $\rightarrow$ Từ chối số tiền vượt ngưỡng để tránh sai lệch tài chính do làm tròn IEEE 754.
 *</t>
+  </si>
+  <si>
+    <t>HTTP 200 OK (Chấp nhận số thực vượt MAX_SAFE_INTEGER)</t>
   </si>
   <si>
     <t>Lý do AI bỏ sót: * AI bỏ qua giới hạn biểu diễn số thực trong JavaScript Engine.</t>
@@ -1360,6 +1420,9 @@
 *</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Lưu trữ an toàn chuỗi CRLF)</t>
+  </si>
+  <si>
     <t>Lý do AI bỏ sót: * AI chỉ tập trung vào SQLi và XSS cơ bản.</t>
   </si>
   <si>
@@ -1376,6 +1439,9 @@
 *</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Gán user_id từ token hợp lệ)</t>
+  </si>
+  <si>
     <t>Lý do AI bỏ sót: * AI bỏ qua kiểm tra rủi ro IDOR ở tầng Request Body khi token đã được xác thực.</t>
   </si>
   <si>
@@ -1392,6 +1458,9 @@
 *</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Lưu trữ an toàn chuỗi Unicode RTL)</t>
+  </si>
+  <si>
     <t>Lý do AI bỏ sót: * AI không tự động sinh payload Unicode Obfuscation nâng cao.</t>
   </si>
   <si>
@@ -1416,6 +1485,9 @@
     <t>Cập nhật trạng thái đơn hàng thành công.</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Cập nhật trạng thái đơn hàng thành công)</t>
+  </si>
+  <si>
     <t>Bao phủ trường hợp hợp lệ với ID đơn hàng tồn tại.</t>
   </si>
   <si>
@@ -1431,6 +1503,9 @@
     <t>Báo lỗi không tìm thấy đơn hàng (Order not found).</t>
   </si>
   <si>
+    <t>HTTP 404 Not Found (Không tìm thấy đơn hàng)</t>
+  </si>
+  <si>
     <t>Kiểm tra xử lý mã định danh không tồn tại.</t>
   </si>
   <si>
@@ -1443,6 +1518,9 @@
     <t>Từ chối ID = 0 không hợp lệ.</t>
   </si>
   <si>
+    <t>HTTP 404 Not Found (Truy vấn CSDL với ID = 0 thay vì báo lỗi 400 - Lỗi B009)</t>
+  </si>
+  <si>
     <t>Kiểm thử giá trị biên số trị 0 cho path parameter.</t>
   </si>
   <si>
@@ -1455,6 +1533,9 @@
     <t>Từ chối ID âm không hợp lệ.</t>
   </si>
   <si>
+    <t>HTTP 404 Not Found (Truy vấn CSDL với ID = -1 thay vì báo lỗi 400 - Lỗi B009)</t>
+  </si>
+  <si>
     <t>Kiểm thử giá trị số âm cho path parameter.</t>
   </si>
   <si>
@@ -1467,6 +1548,9 @@
     <t>Từ chối ID chuỗi ký tự chữ.</t>
   </si>
   <si>
+    <t>HTTP 404 Not Found (Truy vấn CSDL với ID = abc thay vì báo lỗi 400 - Lỗi B009)</t>
+  </si>
+  <si>
     <t>Kiểm thử ép kiểu dữ liệu schema cho path parameter.</t>
   </si>
   <si>
@@ -1479,6 +1563,9 @@
     <t>Từ chối ID số thực dấu phẩy động.</t>
   </si>
   <si>
+    <t>HTTP 400 Bad Request (Từ chối chuyển trạng thái bất hợp lệ)</t>
+  </si>
+  <si>
     <t>Kiểm thử kiểu số nguyên nghiêm ngặt (Strict Integer).</t>
   </si>
   <si>
@@ -1731,6 +1818,9 @@
     <t>Trả về HTTP 403 Forbidden do sai chữ ký JWT.</t>
   </si>
   <si>
+    <t>HTTP 403 Forbidden (Từ chối truy cập đúng phân quyền)</t>
+  </si>
+  <si>
     <t>Kiểm tra từ chối token giả mạo chữ ký.</t>
   </si>
   <si>
@@ -1755,6 +1845,9 @@
     <t>Từ chối User thường sửa trạng thái đơn (Phát hiện lỗi B007).</t>
   </si>
   <si>
+    <t>HTTP 200 OK (User thường cập nhật được trạng thái đơn hàng của Admin - Lỗ hổng B007)</t>
+  </si>
+  <si>
     <t>Kiểm tra kiểm soát truy cập RBAC Admin (SEC-03).</t>
   </si>
   <si>
@@ -1765,6 +1858,9 @@
   </si>
   <si>
     <t>Từ chối User thường xem toàn bộ đơn hàng (Phát hiện lỗi B007).</t>
+  </si>
+  <si>
+    <t>HTTP 200 OK (User thường xem được danh sách đơn hàng của Admin - Lỗ hổng B007)</t>
   </si>
   <si>
     <t>Kiểm tra phân quyền bảo vệ danh sách đơn hàng Admin.</t>
@@ -1897,6 +1993,9 @@
 *</t>
   </si>
   <si>
+    <t>HTTP 200 OK (Cho phép đơn đã hủy canceled chuyển sang delivered - Lỗi B008)</t>
+  </si>
+  <si>
     <t>Lý do AI bỏ sót: * AI thông thường chỉ kiểm tra các bước chuyển xuôi chuẩn mực, bỏ qua kiểm thử rủi ro logic sai sót do lập trình viên cấu hình nhầm điều kiện.</t>
   </si>
   <si>
@@ -1913,6 +2012,9 @@
 *</t>
   </si>
   <si>
+    <t>HTTP 200 OK &amp; 400 Bad Request (Xung đột trạng thái tương tranh)</t>
+  </si>
+  <si>
     <t>Lý do AI bỏ sót: * AI chỉ sinh kịch bản đơn luồng, bỏ qua xung đột tương tranh.</t>
   </si>
   <si>
@@ -1929,6 +2031,9 @@
 *</t>
   </si>
   <si>
+    <t>HTTP 400 Bad Request (Từ chối enum status không hợp lệ)</t>
+  </si>
+  <si>
     <t>Lý do AI bỏ sót: * AI bỏ qua kiểm tra ranh giới enum chặt chẽ cho trường trạng thái.</t>
   </si>
   <si>
@@ -1945,6 +2050,9 @@
 *</t>
   </si>
   <si>
+    <t>HTTP 403 Forbidden (Chặn user thường sửa đơn hàng khi có requireAdmin)</t>
+  </si>
+  <si>
     <t>Lý do AI bỏ sót: * AI bỏ qua kịch bản kết hợp IDOR và RBAC Admin.</t>
   </si>
   <si>
@@ -1965,6 +2073,9 @@
   <si>
     <t xml:space="preserve">Xử lý an toàn số nguyên vượt ngưỡng an toàn trong JavaScript mà không làm sập tiến trình backend.
 *</t>
+  </si>
+  <si>
+    <t>HTTP 404 Not Found (Xử lý an toàn ID vượt MAX_SAFE_INTEGER)</t>
   </si>
   <si>
     <t>Lý do AI bỏ sót: * AI bỏ qua giới hạn biểu diễn số nguyên Number.MAX_SAFE_INTEGER.</t>
@@ -3050,19 +3161,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="5" max="5" width="48" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
+    <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="6" max="6" width="48" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>66</v>
       </c>
@@ -3084,925 +3196,1048 @@
       <c r="G1" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="C3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F2" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G2" s="6" t="s">
+      <c r="E3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="G3" s="7" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E15" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>129</v>
-      </c>
       <c r="C21" s="7" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E22" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B23" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="F22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="C23" s="7" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>78</v>
+        <v>169</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>78</v>
+        <v>174</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>185</v>
-      </c>
       <c r="C29" s="7" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>197</v>
+        <v>79</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>201</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C31" s="7" t="s">
+        <v>205</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="G41" s="7" t="s">
         <v>201</v>
       </c>
-      <c r="D31" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>212</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>213</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>222</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>226</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>222</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>228</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>246</v>
+      <c r="H41" s="7" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -4013,21 +4248,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="45" customWidth="1"/>
+    <col min="3" max="4" width="22" customWidth="1"/>
+    <col min="5" max="5" width="42" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="48" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>66</v>
       </c>
@@ -4035,13 +4270,13 @@
         <v>67</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>69</v>
@@ -4055,1310 +4290,1448 @@
       <c r="I1" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>78</v>
+        <v>262</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D3" s="7" t="s">
-        <v>253</v>
-      </c>
       <c r="E3" s="7" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>78</v>
+        <v>262</v>
       </c>
       <c r="I3" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="I4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="6" t="s">
+      <c r="E5" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="H4" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I4" s="6" t="s">
+      <c r="C6" s="6" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C5" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="E6" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>273</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="E8" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>282</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="E9" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="H8" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="C10" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="F11" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="G11" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="E12" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>290</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="C11" s="7" t="s">
+      <c r="E13" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D11" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>297</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C12" s="6" t="s">
+      <c r="E14" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>299</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="E15" s="7" t="s">
+        <v>322</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+      <c r="E16" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="I16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D17" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="6" t="s">
+      <c r="E17" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="C18" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>314</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C16" s="6" t="s">
+      <c r="E18" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="C17" s="7" t="s">
+      <c r="E19" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D17" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>319</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="C18" s="6" t="s">
+      <c r="E20" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D21" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D18" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="E21" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>350</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="H24" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
+      <c r="E25" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G25" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="H25" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D26" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I20" s="6" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="E26" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D21" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>339</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C22" s="6" t="s">
+      <c r="E27" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>340</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>341</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C23" s="7" t="s">
+      <c r="E28" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>384</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>394</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>396</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>404</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>345</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="E34" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>348</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C25" s="7" t="s">
+      <c r="E35" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D25" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="E36" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>355</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="E37" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="D38" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D27" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>360</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="C28" s="6" t="s">
+      <c r="E38" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D39" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D28" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>363</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>366</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I31" s="7" t="s">
+      <c r="E39" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E42" s="6" t="s">
         <v>383</v>
       </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="C32" s="6" t="s">
+      <c r="F42" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D43" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D32" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>376</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>386</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C34" s="6" t="s">
+      <c r="E43" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>458</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D44" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D34" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>393</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>394</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C35" s="7" t="s">
+      <c r="E44" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="D45" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="D35" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C36" s="6" t="s">
+      <c r="E45" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="H45" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="I45" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D46" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D36" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>402</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>406</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>409</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>405</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>410</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>411</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>412</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>419</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>420</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>421</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>422</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>430</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>433</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>441</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>442</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>443</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="I45" s="7" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>452</v>
-      </c>
-      <c r="B46" s="6" t="s">
+      <c r="E46" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="I46" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="I46" s="6" t="s">
-        <v>456</v>
+      <c r="J46" s="6" t="s">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -5369,19 +5742,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="38" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="36" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
-    <col min="7" max="7" width="48" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="48" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
+    <col min="8" max="8" width="48" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>66</v>
       </c>
@@ -5389,13 +5764,13 @@
         <v>67</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>457</v>
+        <v>480</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>458</v>
+        <v>481</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>69</v>
@@ -5409,1310 +5784,1448 @@
       <c r="I1" s="5" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>459</v>
+        <v>482</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>463</v>
+        <v>486</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>78</v>
+        <v>487</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="3" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>465</v>
+        <v>489</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>466</v>
+        <v>490</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>468</v>
+        <v>492</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>78</v>
+        <v>493</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>470</v>
+        <v>495</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>471</v>
+        <v>496</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>472</v>
+        <v>497</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>475</v>
+        <v>501</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>476</v>
+        <v>502</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>78</v>
+        <v>503</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>78</v>
+        <v>508</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>482</v>
+        <v>510</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>483</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="D9" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="H7" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I7" s="7" t="s">
+      <c r="E9" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>528</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="8" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>486</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="F14" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>487</v>
       </c>
-      <c r="D8" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>488</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>493</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="10" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>495</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>497</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="11" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>499</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>491</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>508</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>509</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="14" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>511</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="I14" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>548</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>513</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>514</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>519</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="16" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>522</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>523</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>524</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="17" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>518</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>528</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="18" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>530</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>532</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>533</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>532</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>78</v>
-      </c>
       <c r="I19" s="7" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="20" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>538</v>
+        <v>567</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>523</v>
+        <v>552</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>539</v>
+        <v>568</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>78</v>
+        <v>513</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="21" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>512</v>
-      </c>
       <c r="C21" s="7" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>542</v>
+        <v>571</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>543</v>
+        <v>572</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>78</v>
+        <v>513</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>545</v>
+        <v>574</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>512</v>
+        <v>541</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>522</v>
+        <v>551</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>532</v>
+        <v>561</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>546</v>
+        <v>575</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>78</v>
+        <v>513</v>
       </c>
       <c r="I22" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="7" t="s">
+        <v>577</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>547</v>
       </c>
-    </row>
-    <row r="23" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>548</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>531</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
+      <c r="F24" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>571</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="H31" s="7" t="s">
+        <v>612</v>
+      </c>
+      <c r="I31" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>618</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>619</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>620</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I33" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="7" t="s">
+        <v>626</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>627</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J35" s="7" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>635</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="I37" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="G38" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>641</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>642</v>
+      </c>
+      <c r="H39" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I39" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="I40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="7" t="s">
+        <v>648</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>649</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="I41" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G42" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="I42" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>660</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>661</v>
+      </c>
+      <c r="H43" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="I43" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="44" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="G44" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="I44" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="45" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="C45" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>512</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>518</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>552</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="26" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>558</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>559</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>371</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="27" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>562</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>563</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="28" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>566</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>567</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>568</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>462</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>574</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>576</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="31" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>578</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>580</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="32" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>583</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>584</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="33" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>588</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="34" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>590</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G34" s="6" t="s">
-        <v>592</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
-        <v>594</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>595</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>596</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>597</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I35" s="7" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="36" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>599</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>579</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G36" s="6" t="s">
-        <v>600</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I36" s="6" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="37" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>579</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I37" s="7" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
+      <c r="D45" s="7" t="s">
         <v>605</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>462</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="G38" s="6" t="s">
-        <v>606</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I38" s="6" t="s">
-        <v>607</v>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
-        <v>608</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="I39" s="7" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="40" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>613</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>614</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="I40" s="6" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="41" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="7" t="s">
-        <v>616</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="F41" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="I41" s="7" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="42" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>619</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>620</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>621</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>622</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G42" s="6" t="s">
-        <v>623</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="I42" s="6" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="7" t="s">
-        <v>625</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>461</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>626</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>627</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>628</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="I43" s="7" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="44" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="6" t="s">
-        <v>630</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>631</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>461</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>632</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="G44" s="6" t="s">
-        <v>633</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>434</v>
-      </c>
-      <c r="I44" s="6" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="7" t="s">
-        <v>635</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>636</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>575</v>
-      </c>
       <c r="E45" s="7" t="s">
-        <v>637</v>
+        <v>672</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>381</v>
+        <v>395</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>638</v>
+        <v>673</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>434</v>
+        <v>674</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="46" ht="30" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="46" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
-        <v>640</v>
+        <v>676</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>641</v>
+        <v>677</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>642</v>
+        <v>678</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>461</v>
+        <v>484</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>643</v>
+        <v>679</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>644</v>
+        <v>680</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>645</v>
+        <v>681</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>434</v>
+        <v>682</v>
       </c>
       <c r="I46" s="6" t="s">
-        <v>646</v>
+        <v>453</v>
+      </c>
+      <c r="J46" s="6" t="s">
+        <v>683</v>
       </c>
     </row>
   </sheetData>
@@ -6737,292 +7250,292 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>647</v>
+        <v>684</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>650</v>
+        <v>687</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>651</v>
+        <v>688</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>652</v>
+        <v>689</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>653</v>
+        <v>690</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>654</v>
+        <v>691</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>655</v>
+        <v>692</v>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>656</v>
+        <v>693</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>657</v>
+        <v>694</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>658</v>
+        <v>695</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>662</v>
+        <v>699</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>664</v>
+        <v>701</v>
       </c>
     </row>
     <row r="3" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>665</v>
+        <v>702</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>666</v>
+        <v>703</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>667</v>
+        <v>704</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>659</v>
+        <v>696</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>662</v>
+        <v>699</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>669</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>670</v>
+        <v>707</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>671</v>
+        <v>708</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>672</v>
+        <v>709</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>674</v>
+        <v>711</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>675</v>
+        <v>712</v>
       </c>
     </row>
     <row r="5" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>676</v>
+        <v>713</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>677</v>
+        <v>714</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>678</v>
+        <v>715</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>674</v>
+        <v>711</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>679</v>
+        <v>716</v>
       </c>
     </row>
     <row r="6" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>680</v>
+        <v>717</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>681</v>
+        <v>718</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>682</v>
+        <v>719</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>674</v>
+        <v>711</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>683</v>
+        <v>720</v>
       </c>
     </row>
     <row r="7" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>684</v>
+        <v>721</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>686</v>
+        <v>723</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>687</v>
+        <v>724</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>674</v>
+        <v>711</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>688</v>
+        <v>725</v>
       </c>
     </row>
     <row r="8" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>689</v>
+        <v>726</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>690</v>
+        <v>727</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>691</v>
+        <v>728</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>692</v>
+        <v>729</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>660</v>
+        <v>697</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>693</v>
+        <v>730</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>694</v>
+        <v>731</v>
       </c>
     </row>
     <row r="9" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>695</v>
+        <v>732</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>696</v>
+        <v>733</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>697</v>
+        <v>734</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>692</v>
+        <v>729</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>668</v>
+        <v>705</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>693</v>
+        <v>730</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>663</v>
+        <v>700</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>698</v>
+        <v>735</v>
       </c>
     </row>
     <row r="10" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>699</v>
+        <v>736</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="H10" s="6" t="s">
         <v>700</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>701</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>692</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>687</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>661</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>693</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>663</v>
-      </c>
       <c r="I10" s="6" t="s">
-        <v>702</v>
+        <v>739</v>
       </c>
     </row>
   </sheetData>
